--- a/results/NMI.xlsx
+++ b/results/NMI.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\427消融实验版\SECT-a-new-method-based-on-louvain-main\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\Desktop\结果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B041EB-3EB9-4A66-A4C8-F27DE413D9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="1690" windowWidth="10520" windowHeight="7700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +81,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -439,14 +438,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -477,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>0.28286099999999997</v>
+        <v>0.266152</v>
       </c>
       <c r="C2" s="1">
         <v>0.97858699999999998</v>
@@ -486,13 +484,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>0.70769000000000004</v>
+        <v>0.72522699999999996</v>
       </c>
       <c r="F2" s="1">
-        <v>0.611568</v>
+        <v>0.60168200000000005</v>
       </c>
       <c r="G2" s="1">
-        <v>0.62198900000000001</v>
+        <v>0.62125699999999995</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -506,16 +504,16 @@
         <v>0.90719799999999995</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>0.99303200000000003</v>
       </c>
       <c r="E3" s="2">
-        <v>0.52220500000000003</v>
+        <v>0.56365299999999996</v>
       </c>
       <c r="F3" s="2">
-        <v>0.55596800000000002</v>
+        <v>0.55501</v>
       </c>
       <c r="G3" s="2">
-        <v>0.481651</v>
+        <v>0.49078699999999997</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -526,7 +524,7 @@
         <v>0.15094199999999999</v>
       </c>
       <c r="C4" s="2">
-        <v>0.21829299999999999</v>
+        <v>0.2636</v>
       </c>
       <c r="D4" s="2">
         <v>4.2251999999999998E-2</v>
@@ -538,7 +536,7 @@
         <v>9.5148999999999997E-2</v>
       </c>
       <c r="G4" s="2">
-        <v>0.12682199999999999</v>
+        <v>0.13067300000000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -546,7 +544,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>0.21251400000000001</v>
+        <v>0.209122</v>
       </c>
       <c r="C5" s="2">
         <v>0.90719799999999995</v>
@@ -555,13 +553,13 @@
         <v>0.99303200000000003</v>
       </c>
       <c r="E5" s="2">
-        <v>0.56766899999999998</v>
+        <v>0.56432700000000002</v>
       </c>
       <c r="F5" s="2">
-        <v>0.555724</v>
+        <v>0.551006</v>
       </c>
       <c r="G5" s="2">
-        <v>0.54959499999999994</v>
+        <v>0.48744399999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -584,7 +582,7 @@
         <v>0.60004999999999997</v>
       </c>
       <c r="G6" s="2">
-        <v>0.56975100000000001</v>
+        <v>0.49650699999999998</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -630,7 +628,7 @@
         <v>0.59670299999999998</v>
       </c>
       <c r="G8" s="2">
-        <v>0.601051</v>
+        <v>0.56817600000000001</v>
       </c>
     </row>
   </sheetData>
